--- a/etf_holdings/2026-09-07_common_holdings_all.xlsx
+++ b/etf_holdings/2026-09-07_common_holdings_all.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>104.04%</t>
+          <t>104.05%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>7.64%</t>
+          <t>8.14%</t>
         </is>
       </c>
       <c r="AD3" t="n">
@@ -986,12 +986,12 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>64.94%</t>
+          <t>65.44%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>5.41%</t>
+          <t>5.45%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="AD4" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>60.90%</t>
+          <t>60.91%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>7.18%</t>
+          <t>6.80%</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>56.60%</t>
+          <t>56.22%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.68%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="AD6" t="n">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>35.60%</t>
+          <t>35.55%</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
